--- a/public/assets/import/IMPORT_EXCEL_INVENTORI.xlsx
+++ b/public/assets/import/IMPORT_EXCEL_INVENTORI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ardhi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5120115A-990A-42AE-9823-6B4D547609EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA07191-5903-4A5D-86A2-FA28B58BA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>TIPE BARANG</t>
   </si>
@@ -48,133 +48,65 @@
     <t>NO AJU (WAJIB SELAIN NON PABEAN)</t>
   </si>
   <si>
-    <t>BAHAN BAKU</t>
-  </si>
-  <si>
-    <t>CANNING</t>
-  </si>
-  <si>
-    <t>WH/CN/0001</t>
-  </si>
-  <si>
     <t>NON PABEAN</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>WH/CN/0002</t>
-  </si>
-  <si>
     <t>BC 4.0</t>
   </si>
   <si>
-    <t>000023-017189-20240212-000010</t>
-  </si>
-  <si>
-    <t>WH/CN/0003</t>
-  </si>
-  <si>
-    <t>000023-017189-20240212-000011</t>
-  </si>
-  <si>
-    <t>WH/CN/0004</t>
-  </si>
-  <si>
-    <t>000023-017189-20240212-000012</t>
-  </si>
-  <si>
-    <t>WH/CN/0005</t>
-  </si>
-  <si>
-    <t>000023-017189-20240212-000013</t>
-  </si>
-  <si>
-    <t>WH/CN/0006</t>
-  </si>
-  <si>
     <t>QTY</t>
   </si>
   <si>
     <t>KATEGORI BARANG</t>
   </si>
   <si>
-    <t>FROZEN</t>
-  </si>
-  <si>
     <t>BAHAN PENOLONG</t>
   </si>
   <si>
-    <t>WORKSHOP</t>
-  </si>
-  <si>
-    <t>SCRAP</t>
-  </si>
-  <si>
-    <t>MESIN</t>
-  </si>
-  <si>
-    <t>KEMASAN</t>
-  </si>
-  <si>
-    <t>BB - 1111</t>
-  </si>
-  <si>
-    <t>BARANG JADI</t>
-  </si>
-  <si>
-    <t>BARANG SCRAP</t>
-  </si>
-  <si>
-    <t>BARANG MODAL</t>
-  </si>
-  <si>
-    <t>BP-0124</t>
-  </si>
-  <si>
-    <t>BJ-0017</t>
-  </si>
-  <si>
-    <t>KEPITING</t>
-  </si>
-  <si>
-    <t>BS-0005</t>
-  </si>
-  <si>
-    <t>BM-0006</t>
-  </si>
-  <si>
-    <t>BP-PJ-001</t>
-  </si>
-  <si>
-    <t>BI-PK-012</t>
-  </si>
-  <si>
-    <t>PACKAGING</t>
-  </si>
-  <si>
-    <t>CANNED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	SCRAP 1</t>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>NAMA SUPPLIER</t>
+  </si>
+  <si>
+    <t>B-BOT-01</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>B-CHL-02</t>
+  </si>
+  <si>
+    <t>Duta Gemini</t>
+  </si>
+  <si>
+    <t>B-FIN-01</t>
+  </si>
+  <si>
+    <t>CV. Sarana Perdana Pratama</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10"/>
@@ -189,8 +121,25 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,8 +152,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -212,11 +167,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,15 +194,28 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,246 +496,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="23.1328125" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="31.46484375" customWidth="1"/>
-    <col min="5" max="5" width="20.265625" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="42.59765625" customWidth="1"/>
-    <col min="8" max="8" width="48.86328125" customWidth="1"/>
+    <col min="7" max="7" width="42.5703125" customWidth="1"/>
+    <col min="8" max="8" width="48.85546875" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>22</v>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3">
-        <v>314</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="8">
+        <v>4</v>
+      </c>
+      <c r="J2" s="9">
+        <v>44927</v>
+      </c>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2">
-        <v>245.5</v>
+      <c r="H3" s="7">
+        <v>608508</v>
+      </c>
+      <c r="I3" s="8">
+        <v>200</v>
+      </c>
+      <c r="J3" s="9">
+        <v>45652</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1">
-        <v>276</v>
-      </c>
-      <c r="E3" s="1" t="s">
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2">
-        <v>204.1</v>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="7">
+        <v>607969</v>
+      </c>
+      <c r="I4" s="8">
+        <v>44</v>
+      </c>
+      <c r="J4" s="9">
+        <v>45629</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="1" t="s">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="E5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="2">
-        <v>167.3</v>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="7">
+        <v>608196</v>
+      </c>
+      <c r="I5" s="8">
+        <v>19</v>
+      </c>
+      <c r="J5" s="9">
+        <v>45638</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2">
-        <v>90.2</v>
+      <c r="G6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="7">
+        <v>605401</v>
+      </c>
+      <c r="I6" s="8">
+        <v>3</v>
+      </c>
+      <c r="J6" s="9">
+        <v>45511</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1223.0999999999999</v>
-      </c>
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="2">
-        <v>2324.1999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>40</v>
-      </c>
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="2">
-        <v>245.5</v>
-      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
